--- a/localisation/references/questionnaireLocalisation.xlsx
+++ b/localisation/references/questionnaireLocalisation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="464">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1380,6 +1380,84 @@
   <si>
     <t xml:space="preserve">Transit</t>
   </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.locationsTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.bothAddresses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les deux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.firstAddressOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logement #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.secondAddressOnly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logement #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.travelTimeTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temps de trajet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.15min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.30min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.45min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.modeOfTransportTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode de transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode of transport</t>
+  </si>
 </sst>
 </file>
 
@@ -1391,7 +1469,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1534,6 +1612,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1625,7 +1709,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1855,6 +1939,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6665,6 +6753,146 @@
         <v>437</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="58" t="s">
+        <v>452</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="58" t="s">
+        <v>455</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B41" s="58" t="s">
+        <v>457</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" s="58" t="s">
+        <v>459</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="58" t="s">
+        <v>461</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
     <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048378" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048379" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/localisation/references/questionnaireLocalisation.xlsx
+++ b/localisation/references/questionnaireLocalisation.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="527">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1117,6 +1117,18 @@
     <t xml:space="preserve">Very burdensome</t>
   </si>
   <si>
+    <t xml:space="preserve">main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loadingMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chargement…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loading…</t>
+  </si>
+  <si>
     <t xml:space="preserve">addGroupedObject</t>
   </si>
   <si>
@@ -1315,6 +1327,129 @@
     <t xml:space="preserve">The estimated number of vehicles for this home is {{predictedCarNumber}}</t>
   </si>
   <si>
+    <t xml:space="preserve">locationComparison.pointsOfInterestTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Points d'intérêt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Points of interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.daycares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garderies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daycares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garderie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daycare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.primarySchools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écoles primaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary schools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">École primaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.secondarySchools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écoles secondaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary schools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">École secondaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.universities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Université</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.hospitals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hôpitaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hôpital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.restaurants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.groceryStores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Épiceries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grocery stores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Épicerie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grocery store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationComparison.shops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop</t>
+  </si>
+  <si>
     <t xml:space="preserve">locationComparison.environmentTitle</t>
   </si>
   <si>
@@ -1322,15 +1457,6 @@
   </si>
   <si>
     <t xml:space="preserve">Environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locationComparison.environmentPointsOfInterest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points d'intérêt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Points of interest</t>
   </si>
   <si>
     <t xml:space="preserve">locationComparison.environmentCo2</t>
@@ -1508,10 +1634,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;VRAI&quot;;&quot;VRAI&quot;;&quot;FAUX&quot;"/>
-    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1739,7 +1866,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1792,6 +1919,10 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1801,6 +1932,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1820,11 +1955,15 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1857,6 +1996,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1900,7 +2043,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1908,11 +2051,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1924,7 +2067,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2256,7 +2399,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.29"/>
@@ -2346,7 +2489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="true" ht="64.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
         <v>25</v>
       </c>
@@ -2381,7 +2524,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="12" t="b">
+      <c r="T2" s="13" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2389,176 +2532,176 @@
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
-      <c r="XEE2" s="14"/>
-      <c r="XEF2" s="14"/>
-      <c r="XEG2" s="14"/>
-      <c r="XEH2" s="14"/>
-      <c r="XEI2" s="14"/>
-      <c r="XEJ2" s="14"/>
-      <c r="XEK2" s="14"/>
-      <c r="XEL2" s="14"/>
-      <c r="XEM2" s="14"/>
-      <c r="XEN2" s="14"/>
-      <c r="XEO2" s="14"/>
-      <c r="XEP2" s="14"/>
-      <c r="XEQ2" s="14"/>
-      <c r="XER2" s="14"/>
-      <c r="XES2" s="14"/>
-      <c r="XET2" s="14"/>
-      <c r="XEU2" s="14"/>
-      <c r="XEV2" s="14"/>
-      <c r="XEW2" s="14"/>
-      <c r="XEX2" s="14"/>
-      <c r="XEY2" s="14"/>
-      <c r="XEZ2" s="14"/>
-      <c r="XFA2" s="14"/>
-      <c r="XFB2" s="14"/>
-      <c r="XFC2" s="14"/>
-      <c r="XFD2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="89.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
+      <c r="XEE2" s="15"/>
+      <c r="XEF2" s="15"/>
+      <c r="XEG2" s="15"/>
+      <c r="XEH2" s="15"/>
+      <c r="XEI2" s="15"/>
+      <c r="XEJ2" s="15"/>
+      <c r="XEK2" s="15"/>
+      <c r="XEL2" s="15"/>
+      <c r="XEM2" s="15"/>
+      <c r="XEN2" s="15"/>
+      <c r="XEO2" s="15"/>
+      <c r="XEP2" s="15"/>
+      <c r="XEQ2" s="15"/>
+      <c r="XER2" s="15"/>
+      <c r="XES2" s="15"/>
+      <c r="XET2" s="15"/>
+      <c r="XEU2" s="15"/>
+      <c r="XEV2" s="15"/>
+      <c r="XEW2" s="15"/>
+      <c r="XEX2" s="15"/>
+      <c r="XEY2" s="15"/>
+      <c r="XEZ2" s="15"/>
+      <c r="XFA2" s="15"/>
+      <c r="XFB2" s="15"/>
+      <c r="XFC2" s="15"/>
+      <c r="XFD2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C3" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15" t="str">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="str">
         <f aca="false">REPLACE(A3, FIND("_", A3), 1, ".")</f>
         <v>household.size</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15" t="s">
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="16"/>
-      <c r="XFD3" s="17"/>
-    </row>
-    <row r="4" customFormat="false" ht="140.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="18"/>
+      <c r="XFD3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="18" t="s">
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="18"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="22" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="5" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="19" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="C5" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21" t="str">
+      <c r="E5" s="23"/>
+      <c r="F5" s="24" t="str">
         <f aca="false">REPLACE(A5, FIND("_", A5), 1, ".")</f>
         <v>home.save</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="19" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
       <c r="XEE5" s="1"/>
       <c r="XEF5" s="1"/>
       <c r="XEG5" s="1"/>
@@ -2584,9 +2727,9 @@
       <c r="XFA5" s="1"/>
       <c r="XFB5" s="1"/>
       <c r="XFC5" s="1"/>
-      <c r="XFD5" s="14"/>
-    </row>
-    <row r="6" s="13" customFormat="true" ht="64.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="XFD5" s="15"/>
+    </row>
+    <row r="6" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>46</v>
       </c>
@@ -2621,7 +2764,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
-      <c r="T6" s="12" t="b">
+      <c r="T6" s="13" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2629,70 +2772,70 @@
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
-      <c r="XEE6" s="14"/>
-      <c r="XEF6" s="14"/>
-      <c r="XEG6" s="14"/>
-      <c r="XEH6" s="14"/>
-      <c r="XEI6" s="14"/>
-      <c r="XEJ6" s="14"/>
-      <c r="XEK6" s="14"/>
-      <c r="XEL6" s="14"/>
-      <c r="XEM6" s="14"/>
-      <c r="XEN6" s="14"/>
-      <c r="XEO6" s="14"/>
-      <c r="XEP6" s="14"/>
-      <c r="XEQ6" s="14"/>
-      <c r="XER6" s="14"/>
-      <c r="XES6" s="14"/>
-      <c r="XET6" s="14"/>
-      <c r="XEU6" s="14"/>
-      <c r="XEV6" s="14"/>
-      <c r="XEW6" s="14"/>
-      <c r="XEX6" s="14"/>
-      <c r="XEY6" s="14"/>
-      <c r="XEZ6" s="14"/>
-      <c r="XFA6" s="14"/>
-      <c r="XFB6" s="14"/>
-      <c r="XFC6" s="14"/>
-      <c r="XFD6" s="23"/>
-    </row>
-    <row r="7" s="16" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="XEE6" s="15"/>
+      <c r="XEF6" s="15"/>
+      <c r="XEG6" s="15"/>
+      <c r="XEH6" s="15"/>
+      <c r="XEI6" s="15"/>
+      <c r="XEJ6" s="15"/>
+      <c r="XEK6" s="15"/>
+      <c r="XEL6" s="15"/>
+      <c r="XEM6" s="15"/>
+      <c r="XEN6" s="15"/>
+      <c r="XEO6" s="15"/>
+      <c r="XEP6" s="15"/>
+      <c r="XEQ6" s="15"/>
+      <c r="XER6" s="15"/>
+      <c r="XES6" s="15"/>
+      <c r="XET6" s="15"/>
+      <c r="XEU6" s="15"/>
+      <c r="XEV6" s="15"/>
+      <c r="XEW6" s="15"/>
+      <c r="XEX6" s="15"/>
+      <c r="XEY6" s="15"/>
+      <c r="XEZ6" s="15"/>
+      <c r="XFA6" s="15"/>
+      <c r="XFB6" s="15"/>
+      <c r="XFC6" s="15"/>
+      <c r="XFD6" s="26"/>
+    </row>
+    <row r="7" s="18" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="C7" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
       <c r="XEE7" s="1"/>
       <c r="XEF7" s="1"/>
       <c r="XEG7" s="1"/>
@@ -2720,57 +2863,57 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" s="16" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+    <row r="8" s="18" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="C8" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="26" t="s">
+      <c r="I8" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="26" t="s">
+      <c r="J8" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29" t="s">
+      <c r="K8" s="29"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
       <c r="XEE8" s="1"/>
       <c r="XEF8" s="1"/>
       <c r="XEG8" s="1"/>
@@ -2798,55 +2941,55 @@
       <c r="XFC8" s="1"/>
       <c r="XFD8" s="1"/>
     </row>
-    <row r="9" s="16" customFormat="true" ht="98.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+    <row r="9" s="18" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="26" t="s">
+      <c r="C9" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29" t="s">
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29" t="s">
+      <c r="N9" s="32"/>
+      <c r="O9" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
       <c r="XEE9" s="1"/>
       <c r="XEF9" s="1"/>
       <c r="XEG9" s="1"/>
@@ -2874,50 +3017,50 @@
       <c r="XFC9" s="1"/>
       <c r="XFD9" s="1"/>
     </row>
-    <row r="10" s="22" customFormat="true" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" s="25" customFormat="true" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="15" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D10" s="26" t="s">
+      <c r="C10" s="17" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21" t="str">
+      <c r="E10" s="23"/>
+      <c r="F10" s="24" t="str">
         <f aca="false">REPLACE(A10, FIND("_", A10), 1, ".")</f>
         <v>household.save</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="19" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="21" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
       <c r="XEE10" s="1"/>
       <c r="XEF10" s="1"/>
       <c r="XEG10" s="1"/>
@@ -2945,7 +3088,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="13" customFormat="true" ht="64.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>68</v>
       </c>
@@ -2980,7 +3123,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="12" t="b">
+      <c r="T11" s="13" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -2988,70 +3131,70 @@
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
-      <c r="XEE11" s="14"/>
-      <c r="XEF11" s="14"/>
-      <c r="XEG11" s="14"/>
-      <c r="XEH11" s="14"/>
-      <c r="XEI11" s="14"/>
-      <c r="XEJ11" s="14"/>
-      <c r="XEK11" s="14"/>
-      <c r="XEL11" s="14"/>
-      <c r="XEM11" s="14"/>
-      <c r="XEN11" s="14"/>
-      <c r="XEO11" s="14"/>
-      <c r="XEP11" s="14"/>
-      <c r="XEQ11" s="14"/>
-      <c r="XER11" s="14"/>
-      <c r="XES11" s="14"/>
-      <c r="XET11" s="14"/>
-      <c r="XEU11" s="14"/>
-      <c r="XEV11" s="14"/>
-      <c r="XEW11" s="14"/>
-      <c r="XEX11" s="14"/>
-      <c r="XEY11" s="14"/>
-      <c r="XEZ11" s="14"/>
-      <c r="XFA11" s="14"/>
-      <c r="XFB11" s="14"/>
-      <c r="XFC11" s="14"/>
+      <c r="XEE11" s="15"/>
+      <c r="XEF11" s="15"/>
+      <c r="XEG11" s="15"/>
+      <c r="XEH11" s="15"/>
+      <c r="XEI11" s="15"/>
+      <c r="XEJ11" s="15"/>
+      <c r="XEK11" s="15"/>
+      <c r="XEL11" s="15"/>
+      <c r="XEM11" s="15"/>
+      <c r="XEN11" s="15"/>
+      <c r="XEO11" s="15"/>
+      <c r="XEP11" s="15"/>
+      <c r="XEQ11" s="15"/>
+      <c r="XER11" s="15"/>
+      <c r="XES11" s="15"/>
+      <c r="XET11" s="15"/>
+      <c r="XEU11" s="15"/>
+      <c r="XEV11" s="15"/>
+      <c r="XEW11" s="15"/>
+      <c r="XEX11" s="15"/>
+      <c r="XEY11" s="15"/>
+      <c r="XEZ11" s="15"/>
+      <c r="XFA11" s="15"/>
+      <c r="XFB11" s="15"/>
+      <c r="XFC11" s="15"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+    <row r="12" s="18" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="26" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="C12" s="33" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
-      <c r="T12" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="27"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
       <c r="XEE12" s="1"/>
       <c r="XEF12" s="1"/>
       <c r="XEG12" s="1"/>
@@ -3079,53 +3222,53 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="16" customFormat="true" ht="142.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+    <row r="13" s="18" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="26" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D13" s="24" t="s">
+      <c r="C13" s="33" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="31" t="s">
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
       <c r="XEE13" s="1"/>
       <c r="XEF13" s="1"/>
       <c r="XEG13" s="1"/>
@@ -3153,53 +3296,53 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="16" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
+    <row r="14" s="18" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="26" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="C14" s="33" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="18" t="s">
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
       <c r="XEE14" s="1"/>
       <c r="XEF14" s="1"/>
       <c r="XEG14" s="1"/>
@@ -3231,70 +3374,70 @@
       <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="26" t="b">
+      <c r="C15" s="33" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="29" t="s">
         <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="30"/>
-      <c r="O15" s="32" t="s">
+      <c r="M15" s="34"/>
+      <c r="O15" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="T15" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T15" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="26" t="b">
+      <c r="C16" s="33" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="30"/>
-      <c r="O16" s="32"/>
-      <c r="T16" s="28" t="n">
+      <c r="M16" s="34"/>
+      <c r="O16" s="36"/>
+      <c r="T16" s="31" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="13" customFormat="true" ht="140.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="14" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
         <v>91</v>
       </c>
@@ -3329,7 +3472,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="12" t="b">
+      <c r="T17" s="13" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3337,105 +3480,105 @@
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
-      <c r="XEE17" s="14"/>
-      <c r="XEF17" s="14"/>
-      <c r="XEG17" s="14"/>
-      <c r="XEH17" s="14"/>
-      <c r="XEI17" s="14"/>
-      <c r="XEJ17" s="14"/>
-      <c r="XEK17" s="14"/>
-      <c r="XEL17" s="14"/>
-      <c r="XEM17" s="14"/>
-      <c r="XEN17" s="14"/>
-      <c r="XEO17" s="14"/>
-      <c r="XEP17" s="14"/>
-      <c r="XEQ17" s="14"/>
-      <c r="XER17" s="14"/>
-      <c r="XES17" s="14"/>
-      <c r="XET17" s="14"/>
-      <c r="XEU17" s="14"/>
-      <c r="XEV17" s="14"/>
-      <c r="XEW17" s="14"/>
-      <c r="XEX17" s="14"/>
-      <c r="XEY17" s="14"/>
-      <c r="XEZ17" s="14"/>
-      <c r="XFA17" s="14"/>
-      <c r="XFB17" s="14"/>
-      <c r="XFC17" s="14"/>
+      <c r="XEE17" s="15"/>
+      <c r="XEF17" s="15"/>
+      <c r="XEG17" s="15"/>
+      <c r="XEH17" s="15"/>
+      <c r="XEI17" s="15"/>
+      <c r="XEJ17" s="15"/>
+      <c r="XEK17" s="15"/>
+      <c r="XEL17" s="15"/>
+      <c r="XEM17" s="15"/>
+      <c r="XEN17" s="15"/>
+      <c r="XEO17" s="15"/>
+      <c r="XEP17" s="15"/>
+      <c r="XEQ17" s="15"/>
+      <c r="XER17" s="15"/>
+      <c r="XES17" s="15"/>
+      <c r="XET17" s="15"/>
+      <c r="XEU17" s="15"/>
+      <c r="XEV17" s="15"/>
+      <c r="XEW17" s="15"/>
+      <c r="XEX17" s="15"/>
+      <c r="XEY17" s="15"/>
+      <c r="XEZ17" s="15"/>
+      <c r="XFA17" s="15"/>
+      <c r="XFB17" s="15"/>
+      <c r="XFC17" s="15"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="23" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
+    <row r="18" s="26" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="34" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D18" s="33" t="s">
+      <c r="C18" s="38" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D18" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="T18" s="34" t="n">
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="T18" s="38" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="16" customFormat="true" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="s">
+    <row r="19" s="18" customFormat="true" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="36" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="40" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31" t="s">
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
       <c r="XEE19" s="1"/>
       <c r="XEF19" s="1"/>
       <c r="XEG19" s="1"/>
@@ -3463,52 +3606,52 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" s="16" customFormat="true" ht="96.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30" t="s">
+    <row r="20" s="18" customFormat="true" ht="96.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="36" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="40" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H20" s="30" t="s">
+      <c r="H20" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="16" t="s">
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="18" t="s">
         <v>104</v>
       </c>
       <c r="XEE20" s="1"/>
@@ -3538,196 +3681,196 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="51.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="C21" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="18" t="s">
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="C22" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="26" t="s">
+      <c r="H22" s="29" t="s">
         <v>113</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O22" s="37"/>
-      <c r="T22" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="s">
+      <c r="O22" s="41"/>
+      <c r="T22" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="C23" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="M23" s="30" t="s">
+      <c r="M23" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="O23" s="38" t="s">
+      <c r="O23" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="T23" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
+      <c r="T23" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="s">
+      <c r="C24" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="H24" s="26" t="s">
+      <c r="H24" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="M24" s="30" t="s">
+      <c r="M24" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="O24" s="38"/>
-      <c r="T24" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
+      <c r="O24" s="42"/>
+      <c r="T24" s="31" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="C25" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="H25" s="26" t="s">
+      <c r="H25" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="M25" s="30" t="s">
+      <c r="M25" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="N25" s="15" t="s">
+      <c r="N25" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="O25" s="38"/>
-      <c r="T25" s="28" t="n">
+      <c r="O25" s="42"/>
+      <c r="T25" s="31" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3735,40 +3878,40 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="s">
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="H26" s="26" t="s">
+      <c r="H26" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="K26" s="15"/>
-      <c r="M26" s="30" t="s">
+      <c r="K26" s="16"/>
+      <c r="M26" s="34" t="s">
         <v>124</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="T26" s="28" t="n">
+      <c r="T26" s="31" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3779,121 +3922,121 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37" t="s">
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="C27" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="H27" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="K27" s="15"/>
-      <c r="M27" s="30" t="s">
+      <c r="K27" s="16"/>
+      <c r="M27" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="T27" s="28" t="n">
+      <c r="T27" s="31" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D28" s="15" t="s">
+      <c r="C28" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="H28" s="26" t="s">
+      <c r="H28" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="M28" s="30" t="s">
+      <c r="M28" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="T28" s="28" t="n">
+      <c r="T28" s="31" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" s="22" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="19" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D29" s="19" t="s">
+      <c r="C29" s="22" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="21" t="str">
+      <c r="E29" s="23"/>
+      <c r="F29" s="24" t="str">
         <f aca="false">REPLACE(A29, FIND("_", A29), 1, ".")</f>
         <v>addresses.save</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="19" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="21" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
       <c r="XEE29" s="1"/>
       <c r="XEF29" s="1"/>
       <c r="XEG29" s="1"/>
@@ -3921,14 +4064,14 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="13" customFormat="true" ht="178.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="14" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="36" t="n">
+      <c r="C30" s="40" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3956,7 +4099,7 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="12" t="b">
+      <c r="T30" s="13" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3964,100 +4107,100 @@
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9"/>
-      <c r="XEE30" s="14"/>
-      <c r="XEF30" s="14"/>
-      <c r="XEG30" s="14"/>
-      <c r="XEH30" s="14"/>
-      <c r="XEI30" s="14"/>
-      <c r="XEJ30" s="14"/>
-      <c r="XEK30" s="14"/>
-      <c r="XEL30" s="14"/>
-      <c r="XEM30" s="14"/>
-      <c r="XEN30" s="14"/>
-      <c r="XEO30" s="14"/>
-      <c r="XEP30" s="14"/>
-      <c r="XEQ30" s="14"/>
-      <c r="XER30" s="14"/>
-      <c r="XES30" s="14"/>
-      <c r="XET30" s="14"/>
-      <c r="XEU30" s="14"/>
-      <c r="XEV30" s="14"/>
-      <c r="XEW30" s="14"/>
-      <c r="XEX30" s="14"/>
-      <c r="XEY30" s="14"/>
-      <c r="XEZ30" s="14"/>
-      <c r="XFA30" s="14"/>
-      <c r="XFB30" s="14"/>
-      <c r="XFC30" s="14"/>
+      <c r="XEE30" s="15"/>
+      <c r="XEF30" s="15"/>
+      <c r="XEG30" s="15"/>
+      <c r="XEH30" s="15"/>
+      <c r="XEI30" s="15"/>
+      <c r="XEJ30" s="15"/>
+      <c r="XEK30" s="15"/>
+      <c r="XEL30" s="15"/>
+      <c r="XEM30" s="15"/>
+      <c r="XEN30" s="15"/>
+      <c r="XEO30" s="15"/>
+      <c r="XEP30" s="15"/>
+      <c r="XEQ30" s="15"/>
+      <c r="XER30" s="15"/>
+      <c r="XES30" s="15"/>
+      <c r="XET30" s="15"/>
+      <c r="XEU30" s="15"/>
+      <c r="XEV30" s="15"/>
+      <c r="XEW30" s="15"/>
+      <c r="XEX30" s="15"/>
+      <c r="XEY30" s="15"/>
+      <c r="XEZ30" s="15"/>
+      <c r="XFA30" s="15"/>
+      <c r="XFB30" s="15"/>
+      <c r="XFC30" s="15"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D31" s="30" t="s">
+      <c r="C31" s="17" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="T31" s="15" t="n">
+      <c r="T31" s="16" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" s="16" customFormat="true" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
+    <row r="32" s="18" customFormat="true" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="36" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="C32" s="40" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31" t="s">
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="35"/>
       <c r="XEE32" s="1"/>
       <c r="XEF32" s="1"/>
       <c r="XEG32" s="1"/>
@@ -4085,52 +4228,52 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" s="16" customFormat="true" ht="96.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="s">
+    <row r="33" s="18" customFormat="true" ht="96.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="36" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="C33" s="40" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="H33" s="30" t="s">
+      <c r="H33" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29"/>
-      <c r="Y33" s="16" t="s">
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="18" t="s">
         <v>104</v>
       </c>
       <c r="XEE33" s="1"/>
@@ -4160,86 +4303,86 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="39.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="39" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="C34" s="43" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="H34" s="26" t="s">
+      <c r="H34" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="K34" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="M34" s="30"/>
-      <c r="T34" s="15" t="n">
+      <c r="M34" s="34"/>
+      <c r="T34" s="16" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="22" customFormat="true" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="19" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="C35" s="22" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="21" t="str">
+      <c r="E35" s="23"/>
+      <c r="F35" s="24" t="str">
         <f aca="false">REPLACE(A35, FIND("_", A35), 1, ".")</f>
         <v>destinations.save</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="19" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="21" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
       <c r="XEE35" s="1"/>
       <c r="XEF35" s="1"/>
       <c r="XEG35" s="1"/>
@@ -4267,21 +4410,21 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="36" t="n">
+      <c r="C36" s="40" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="16" t="s">
         <v>164</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -4290,19 +4433,19 @@
       <c r="H36" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="T36" s="15" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T36" s="16" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="36" t="n">
+      <c r="C37" s="40" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4362,48 +4505,48 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="38.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="15.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="40" width="20.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="12.14"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="30" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="38.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="44" width="20.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="34" width="19.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="12.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="34" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="45" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="30" t="n">
+      <c r="E2" s="34" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4639,196 +4782,196 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="10.69921875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.69921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="13.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="12.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="30" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="30" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="15.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="30" width="10.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="34" width="12.57"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="34" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="34" width="15.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="34" width="10.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="48" t="s">
         <v>182</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="48" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F2" s="46" t="b">
+      <c r="E2" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G2" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
+      <c r="G2" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="46" t="b">
+      <c r="E3" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G3" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
+      <c r="G3" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="E4" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="46" t="b">
+      <c r="E4" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G4" s="46" t="b">
+      <c r="G4" s="50" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="46" t="b">
+      <c r="E5" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G5" s="46" t="b">
+      <c r="G5" s="50" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="E6" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="46" t="b">
+      <c r="E6" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G6" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
+      <c r="G6" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="46" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="46" t="b">
+      <c r="E7" s="50" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="50" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G7" s="46" t="b">
+      <c r="G7" s="50" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5019,385 +5162,385 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="29.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="30.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="24.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="32" width="24.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="32" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="36" width="29.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="36" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="36" width="30.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="36" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="36" width="24.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="36" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="36" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="H8" s="38"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38" t="s">
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="H9" s="38"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38" t="s">
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="38"/>
+      <c r="H10" s="42"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38" t="s">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="H11" s="38"/>
+      <c r="H11" s="42"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="H12" s="38"/>
+      <c r="H12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="H13" s="38"/>
+      <c r="H13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38" t="s">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="H14" s="38"/>
+      <c r="H14" s="42"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="42" t="s">
         <v>228</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="H17" s="38"/>
+      <c r="H17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38" t="s">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="H21" s="38"/>
+      <c r="H21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="36" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -5413,7 +5556,7 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -5429,7 +5572,7 @@
       <c r="F24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5445,7 +5588,7 @@
       <c r="F25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -5461,7 +5604,7 @@
       <c r="F26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -5477,7 +5620,7 @@
       <c r="F27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5493,7 +5636,7 @@
       <c r="F28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -5509,7 +5652,7 @@
       <c r="F29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -5525,7 +5668,7 @@
       <c r="F30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5541,7 +5684,7 @@
       <c r="F31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -5557,7 +5700,7 @@
       <c r="F32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -5573,7 +5716,7 @@
       <c r="F33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -5589,7 +5732,7 @@
       <c r="F34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -5605,184 +5748,184 @@
       <c r="F35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="36" t="s">
         <v>281</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="36" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="36" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="36" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="36" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="36" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="36" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="36" t="s">
         <v>298</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="36" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="36" t="s">
         <v>301</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="36" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="G44" s="38" t="s">
+      <c r="G44" s="42" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="H45" s="30"/>
+      <c r="H45" s="34"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="H46" s="30"/>
+      <c r="H46" s="34"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="C47" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="H47" s="30"/>
+      <c r="H47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="H48" s="30"/>
+      <c r="H48" s="34"/>
     </row>
     <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5978,7 +6121,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.71"/>
@@ -5993,192 +6136,192 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="54" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="54" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="54" t="s">
         <v>319</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="54" t="s">
         <v>320</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="54" t="s">
         <v>322</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="54" t="s">
         <v>324</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="54" t="s">
         <v>325</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="55" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="H2" s="18" t="n">
+      <c r="H2" s="20" t="n">
         <v>-10</v>
       </c>
-      <c r="I2" s="18" t="n">
+      <c r="I2" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="20" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="56" t="s">
         <v>339</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="20" t="n">
         <v>-10</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="20" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="20" t="n">
         <v>-10</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="20" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="20" t="n">
         <v>-10</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="20" t="s">
         <v>335</v>
       </c>
     </row>
@@ -6311,7 +6454,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="33.83"/>
@@ -6342,170 +6485,172 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>356</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="C3" s="4" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D4" s="4" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D6" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="34" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D7" s="4" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="34" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>373</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="57" t="s">
         <v>377</v>
       </c>
+      <c r="C10" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>386</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6513,13 +6658,13 @@
         <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D14" s="2" t="s">
         <v>389</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6527,69 +6672,69 @@
         <v>165</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D16" s="30" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D17" s="1" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="34" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>399</v>
+      <c r="B18" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>402</v>
+      <c r="B19" s="34" t="s">
+        <v>403</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6597,13 +6742,13 @@
         <v>165</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6611,13 +6756,13 @@
         <v>165</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6625,13 +6770,13 @@
         <v>165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6639,13 +6784,13 @@
         <v>165</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6653,13 +6798,13 @@
         <v>165</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6667,13 +6812,13 @@
         <v>165</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6681,13 +6826,13 @@
         <v>165</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6695,13 +6840,13 @@
         <v>165</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6709,13 +6854,19 @@
         <v>165</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C28" s="2" t="s">
         <v>429</v>
       </c>
+      <c r="C28" s="1" t="s">
+        <v>430</v>
+      </c>
       <c r="D28" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6723,145 +6874,181 @@
         <v>165</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>433</v>
+      <c r="B30" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>437</v>
+      <c r="B31" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>441</v>
+      <c r="B32" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>442</v>
+      <c r="B33" s="2" t="s">
+        <v>454</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>445</v>
+      <c r="B34" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>447</v>
+        <v>459</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>448</v>
+      <c r="B35" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>295</v>
+        <v>463</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>449</v>
+        <v>464</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>450</v>
+      <c r="B36" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>455</v>
+      <c r="B37" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>457</v>
+      <c r="B38" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6869,13 +7056,19 @@
         <v>165</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>459</v>
+        <v>198</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>460</v>
+        <v>476</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6883,13 +7076,13 @@
         <v>165</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6897,13 +7090,13 @@
         <v>165</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>465</v>
+        <v>482</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>483</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6911,13 +7104,13 @@
         <v>165</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>469</v>
+        <v>485</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6925,13 +7118,13 @@
         <v>165</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>471</v>
+        <v>488</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6939,13 +7132,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>473</v>
+        <v>295</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6953,13 +7146,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6967,13 +7160,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6981,13 +7174,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6995,24 +7188,141 @@
         <v>165</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="1048380" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048381" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048382" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048383" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048384" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048385" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048386" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048387" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048388" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
     <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/localisation/references/questionnaireLocalisation.xlsx
+++ b/localisation/references/questionnaireLocalisation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="550">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1291,6 +1291,15 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
+    <t xml:space="preserve">locationComparison.timeTotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temps de transport en commun vers les destinations fréquentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public transport time to frequent destinations</t>
+  </si>
+  <si>
     <t xml:space="preserve">locationComparison.costsPercentageOfIncome</t>
   </si>
   <si>
@@ -1628,6 +1637,66 @@
   </si>
   <si>
     <t xml:space="preserve">Expand the panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.lessThanOneMin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 1 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{count}} min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{hours}} h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.hoursMinutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{hours}} h {{minutes}} min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.oneDay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{count}} jours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{count}} days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.oneDayHours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 jour {{hours}} h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 day {{hours}} h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeFormat.daysHours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{days}} jours {{hours}} h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{days}} days {{hours}} h</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1709,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1775,6 +1844,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1866,7 +1941,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2096,6 +2171,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6786,10 +6873,10 @@
       <c r="B23" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>416</v>
       </c>
     </row>
@@ -6862,31 +6949,25 @@
       <c r="D28" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>433</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6894,19 +6975,19 @@
         <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6914,19 +6995,19 @@
         <v>165</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6934,19 +7015,19 @@
         <v>165</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6954,16 +7035,16 @@
         <v>165</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>456</v>
@@ -6980,13 +7061,13 @@
         <v>458</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6994,19 +7075,19 @@
         <v>165</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7014,12 +7095,18 @@
         <v>165</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>469</v>
       </c>
     </row>
@@ -7030,11 +7117,11 @@
       <c r="B37" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>471</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7042,10 +7129,10 @@
         <v>165</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>474</v>
@@ -7055,20 +7142,14 @@
       <c r="A39" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7076,12 +7157,18 @@
         <v>165</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>481</v>
       </c>
     </row>
@@ -7092,11 +7179,11 @@
       <c r="B41" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>483</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7104,12 +7191,12 @@
         <v>165</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C42" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>486</v>
       </c>
     </row>
@@ -7135,10 +7222,10 @@
         <v>490</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>295</v>
+        <v>491</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7146,10 +7233,10 @@
         <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>493</v>
+        <v>295</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>494</v>
@@ -7165,7 +7252,7 @@
       <c r="C46" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>497</v>
       </c>
     </row>
@@ -7177,10 +7264,10 @@
         <v>498</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>407</v>
+        <v>499</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7188,10 +7275,10 @@
         <v>165</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>501</v>
+        <v>407</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>502</v>
@@ -7250,7 +7337,7 @@
         <v>513</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7258,13 +7345,13 @@
         <v>165</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7272,13 +7359,13 @@
         <v>165</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7286,10 +7373,10 @@
         <v>165</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>520</v>
@@ -7323,7 +7410,132 @@
         <v>526</v>
       </c>
     </row>
-    <row r="1048389" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" s="58" t="s">
+        <v>530</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>531</v>
+      </c>
+      <c r="D59" s="58" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" s="59" t="s">
+        <v>532</v>
+      </c>
+      <c r="C60" s="59" t="s">
+        <v>533</v>
+      </c>
+      <c r="D60" s="59" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="59" t="s">
+        <v>534</v>
+      </c>
+      <c r="C61" s="59" t="s">
+        <v>535</v>
+      </c>
+      <c r="D61" s="59" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B62" s="59" t="s">
+        <v>536</v>
+      </c>
+      <c r="C62" s="59" t="s">
+        <v>537</v>
+      </c>
+      <c r="D62" s="59" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="59" t="s">
+        <v>538</v>
+      </c>
+      <c r="C63" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="D63" s="59" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="59" t="s">
+        <v>541</v>
+      </c>
+      <c r="C64" s="60" t="s">
+        <v>542</v>
+      </c>
+      <c r="D64" s="60" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="C65" s="59" t="s">
+        <v>545</v>
+      </c>
+      <c r="D65" s="59" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="59" t="s">
+        <v>547</v>
+      </c>
+      <c r="C66" s="59" t="s">
+        <v>548</v>
+      </c>
+      <c r="D66" s="59" t="s">
+        <v>549</v>
+      </c>
+    </row>
     <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/localisation/references/questionnaireLocalisation.xlsx
+++ b/localisation/references/questionnaireLocalisation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="574">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1637,6 +1637,78 @@
   </si>
   <si>
     <t xml:space="preserve">Expand the panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.departureTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heure de départ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departure time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.8am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.12pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.5pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.10pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.weekend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fin de semaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accessibilityPanel.noTransitWarningMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notez que l’heure de départ n’a pas d’effet pour les modes autres que le transport collectif.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note that the departure time will have no effect for modes other than transit.</t>
   </si>
   <si>
     <t xml:space="preserve">timeFormat.lessThanOneMin</t>
@@ -1703,13 +1775,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;VRAI&quot;;&quot;VRAI&quot;;&quot;FAUX&quot;"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="@"/>
+    <numFmt numFmtId="168" formatCode="[$-C0C]General"/>
+    <numFmt numFmtId="169" formatCode="[$-C0C]@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1844,12 +1918,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1941,7 +2009,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2170,19 +2238,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2499,7 +2579,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="10.91"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2576,7 +2656,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="14" customFormat="true" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2726,7 @@
       <c r="XFC2" s="15"/>
       <c r="XFD2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
         <v>30</v>
       </c>
@@ -2697,7 +2777,7 @@
       <c r="Y3" s="18"/>
       <c r="XFD3" s="19"/>
     </row>
-    <row r="4" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
@@ -2745,7 +2825,7 @@
       <c r="Y4" s="18"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="25" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
         <v>42</v>
       </c>
@@ -2816,7 +2896,7 @@
       <c r="XFC5" s="1"/>
       <c r="XFD5" s="15"/>
     </row>
-    <row r="6" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" s="14" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>46</v>
       </c>
@@ -2886,7 +2966,7 @@
       <c r="XFC6" s="15"/>
       <c r="XFD6" s="26"/>
     </row>
-    <row r="7" s="18" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="18" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
         <v>50</v>
       </c>
@@ -2950,7 +3030,7 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" s="18" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="18" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
         <v>52</v>
       </c>
@@ -3028,7 +3108,7 @@
       <c r="XFC8" s="1"/>
       <c r="XFD8" s="1"/>
     </row>
-    <row r="9" s="18" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="18" customFormat="true" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
         <v>60</v>
       </c>
@@ -3175,7 +3255,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="14" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="14" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>68</v>
       </c>
@@ -3309,7 +3389,7 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="18" customFormat="true" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="18" customFormat="true" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
         <v>73</v>
       </c>
@@ -3383,7 +3463,7 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="18" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="18" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>79</v>
       </c>
@@ -3457,7 +3537,7 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
@@ -3492,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -3524,7 +3604,7 @@
       </c>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="14" customFormat="true" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="14" customFormat="true" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
         <v>91</v>
       </c>
@@ -3594,7 +3674,7 @@
       <c r="XFC17" s="15"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="26" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="26" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
         <v>95</v>
       </c>
@@ -3768,7 +3848,7 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
         <v>105</v>
       </c>
@@ -3817,7 +3897,7 @@
       <c r="X21" s="16"/>
       <c r="Y21" s="18"/>
     </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="41" t="s">
         <v>110</v>
       </c>
@@ -3852,7 +3932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="41" t="s">
         <v>115</v>
       </c>
@@ -3924,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="41" t="s">
         <v>125</v>
       </c>
@@ -3965,7 +4045,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="41" t="s">
         <v>131</v>
       </c>
@@ -4009,7 +4089,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="41" t="s">
         <v>137</v>
       </c>
@@ -4045,7 +4125,7 @@
       </c>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
@@ -4080,7 +4160,7 @@
       </c>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="25" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
         <v>146</v>
       </c>
@@ -4151,7 +4231,7 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="14" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="14" customFormat="true" ht="243.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>147</v>
       </c>
@@ -4390,7 +4470,7 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>158</v>
       </c>
@@ -4426,7 +4506,7 @@
       </c>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="25" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="25" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
         <v>163</v>
       </c>
@@ -4603,7 +4683,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="34" width="8.59"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
         <v>171</v>
       </c>
@@ -6222,7 +6302,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="24.39"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
         <v>315</v>
       </c>
@@ -6544,7 +6624,8 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="33.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="41.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="57" width="33.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.91"/>
@@ -6557,7 +6638,7 @@
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="58" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -6577,7 +6658,7 @@
       <c r="B2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="58" t="s">
         <v>358</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -6593,7 +6674,7 @@
       <c r="B3" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="58" t="s">
         <v>361</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -6607,7 +6688,7 @@
       <c r="B4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="59" t="s">
         <v>364</v>
       </c>
       <c r="D4" s="34" t="s">
@@ -6621,7 +6702,7 @@
       <c r="B5" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="58" t="s">
         <v>366</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -6635,7 +6716,7 @@
       <c r="B6" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="59" t="s">
         <v>368</v>
       </c>
       <c r="D6" s="34" t="s">
@@ -6649,21 +6730,21 @@
       <c r="B7" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="59" t="s">
         <v>371</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="58" t="s">
         <v>373</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -6677,7 +6758,7 @@
       <c r="B9" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="59" t="s">
         <v>375</v>
       </c>
       <c r="D9" s="34" t="s">
@@ -6688,10 +6769,10 @@
       <c r="A10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="60" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="59" t="s">
         <v>378</v>
       </c>
       <c r="D10" s="34" t="s">
@@ -6705,7 +6786,7 @@
       <c r="B11" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="57" t="s">
         <v>380</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -6719,21 +6800,21 @@
       <c r="B12" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="57" t="s">
         <v>383</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="61" t="s">
         <v>386</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -6747,7 +6828,7 @@
       <c r="B14" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="57" t="s">
         <v>389</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -6761,7 +6842,7 @@
       <c r="B15" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="57" t="s">
         <v>392</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -6775,7 +6856,7 @@
       <c r="B16" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="57" t="s">
         <v>395</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -6789,7 +6870,7 @@
       <c r="B17" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="57" t="s">
         <v>398</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -6803,7 +6884,7 @@
       <c r="B18" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="57" t="s">
         <v>401</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -6817,7 +6898,7 @@
       <c r="B19" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="57" t="s">
         <v>404</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -6831,7 +6912,7 @@
       <c r="B20" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="57" t="s">
         <v>407</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -6845,7 +6926,7 @@
       <c r="B21" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="57" t="s">
         <v>410</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -6859,7 +6940,7 @@
       <c r="B22" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="57" t="s">
         <v>413</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -6873,7 +6954,7 @@
       <c r="B23" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="61" t="s">
         <v>415</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -6887,7 +6968,7 @@
       <c r="B24" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="57" t="s">
         <v>418</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -6901,7 +6982,7 @@
       <c r="B25" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="57" t="s">
         <v>421</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -6915,7 +6996,7 @@
       <c r="B26" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="57" t="s">
         <v>424</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -6929,7 +7010,7 @@
       <c r="B27" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="57" t="s">
         <v>427</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -6943,7 +7024,7 @@
       <c r="B28" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="57" t="s">
         <v>430</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -6957,7 +7038,7 @@
       <c r="B29" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="57" t="s">
         <v>433</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -6977,7 +7058,7 @@
       <c r="B30" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="57" t="s">
         <v>438</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -6997,7 +7078,7 @@
       <c r="B31" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="57" t="s">
         <v>443</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -7017,7 +7098,7 @@
       <c r="B32" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="57" t="s">
         <v>448</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -7037,7 +7118,7 @@
       <c r="B33" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="57" t="s">
         <v>453</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -7057,7 +7138,7 @@
       <c r="B34" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="57" t="s">
         <v>458</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -7077,7 +7158,7 @@
       <c r="B35" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="57" t="s">
         <v>461</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -7097,7 +7178,7 @@
       <c r="B36" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="57" t="s">
         <v>466</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -7117,7 +7198,7 @@
       <c r="B37" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="57" t="s">
         <v>471</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -7131,7 +7212,7 @@
       <c r="B38" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="61" t="s">
         <v>474</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -7145,7 +7226,7 @@
       <c r="B39" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="61" t="s">
         <v>476</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -7159,7 +7240,7 @@
       <c r="B40" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="57" t="s">
         <v>198</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -7179,7 +7260,7 @@
       <c r="B41" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="57" t="s">
         <v>483</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -7193,7 +7274,7 @@
       <c r="B42" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="61" t="s">
         <v>486</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -7207,7 +7288,7 @@
       <c r="B43" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="57" t="s">
         <v>488</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -7221,7 +7302,7 @@
       <c r="B44" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="57" t="s">
         <v>491</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -7235,7 +7316,7 @@
       <c r="B45" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="57" t="s">
         <v>295</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -7249,7 +7330,7 @@
       <c r="B46" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="57" t="s">
         <v>496</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -7263,7 +7344,7 @@
       <c r="B47" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="57" t="s">
         <v>499</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -7277,7 +7358,7 @@
       <c r="B48" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="57" t="s">
         <v>407</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -7291,7 +7372,7 @@
       <c r="B49" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="57" t="s">
         <v>504</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -7305,7 +7386,7 @@
       <c r="B50" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="57" t="s">
         <v>507</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -7319,7 +7400,7 @@
       <c r="B51" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="57" t="s">
         <v>510</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -7333,7 +7414,7 @@
       <c r="B52" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="57" t="s">
         <v>513</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -7347,7 +7428,7 @@
       <c r="B53" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="57" t="s">
         <v>516</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -7361,7 +7442,7 @@
       <c r="B54" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="57" t="s">
         <v>518</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -7375,7 +7456,7 @@
       <c r="B55" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="57" t="s">
         <v>520</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -7389,7 +7470,7 @@
       <c r="B56" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="57" t="s">
         <v>522</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -7403,7 +7484,7 @@
       <c r="B57" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="57" t="s">
         <v>525</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -7417,133 +7498,237 @@
       <c r="B58" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="57" t="s">
         <v>528</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B59" s="58" t="s">
+      <c r="B59" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="57" t="s">
         <v>531</v>
       </c>
-      <c r="D59" s="58" t="s">
-        <v>531</v>
+      <c r="D59" s="1" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B60" s="59" t="s">
-        <v>532</v>
-      </c>
-      <c r="C60" s="59" t="s">
+      <c r="B60" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D60" s="59" t="s">
-        <v>533</v>
+      <c r="C60" s="62" t="s">
+        <v>534</v>
+      </c>
+      <c r="D60" s="63" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B61" s="59" t="s">
-        <v>534</v>
-      </c>
-      <c r="C61" s="59" t="s">
-        <v>535</v>
-      </c>
-      <c r="D61" s="59" t="s">
-        <v>535</v>
+      <c r="B61" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C61" s="62" t="s">
+        <v>537</v>
+      </c>
+      <c r="D61" s="63" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="59" t="s">
-        <v>536</v>
-      </c>
-      <c r="C62" s="59" t="s">
-        <v>537</v>
-      </c>
-      <c r="D62" s="59" t="s">
-        <v>537</v>
+      <c r="B62" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C62" s="62" t="s">
+        <v>540</v>
+      </c>
+      <c r="D62" s="63" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B63" s="59" t="s">
-        <v>538</v>
-      </c>
-      <c r="C63" s="59" t="s">
-        <v>539</v>
-      </c>
-      <c r="D63" s="59" t="s">
-        <v>540</v>
+      <c r="B63" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C63" s="62" t="s">
+        <v>543</v>
+      </c>
+      <c r="D63" s="63" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B64" s="59" t="s">
-        <v>541</v>
-      </c>
-      <c r="C64" s="60" t="s">
-        <v>542</v>
-      </c>
-      <c r="D64" s="60" t="s">
-        <v>543</v>
+      <c r="B64" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C64" s="57" t="s">
+        <v>546</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B65" s="59" t="s">
-        <v>544</v>
-      </c>
-      <c r="C65" s="59" t="s">
-        <v>545</v>
-      </c>
-      <c r="D65" s="59" t="s">
-        <v>546</v>
+      <c r="B65" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C65" s="57" t="s">
+        <v>549</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B66" s="59" t="s">
-        <v>547</v>
-      </c>
-      <c r="C66" s="59" t="s">
-        <v>548</v>
-      </c>
-      <c r="D66" s="59" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="1048390" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048391" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048392" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048393" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048394" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048395" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048396" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048397" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="B66" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>552</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="C67" s="59" t="s">
+        <v>555</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C68" s="61" t="s">
+        <v>557</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C69" s="61" t="s">
+        <v>559</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C70" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C71" s="61" t="s">
+        <v>563</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C72" s="61" t="s">
+        <v>566</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C73" s="61" t="s">
+        <v>569</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>572</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
     <row r="1048398" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048399" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048400" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/localisation/references/questionnaireLocalisation.xlsx
+++ b/localisation/references/questionnaireLocalisation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -394,10 +394,10 @@
     <t xml:space="preserve">areUtilitiesIncluded</t>
   </si>
   <si>
-    <t xml:space="preserve">**Le prix des services publics** (électricité, gaz, ...) **est-il inclus dans le loyer?**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Is the cost of utilities** (electricity, gas, ...) **included in the rent?**</t>
+    <t xml:space="preserve">**Le prix des services publics** (électricité, gaz, parking, ...) **est-il inclus dans le loyer?**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Is the cost of utilities** (electricity, gas, parking, ...) **included in the rent?**</t>
   </si>
   <si>
     <t xml:space="preserve">yesNo</t>
@@ -472,10 +472,10 @@
     <t xml:space="preserve">utilitiesMonthly</t>
   </si>
   <si>
-    <t xml:space="preserve">**Montant mensuel des services publics** (électricité, gaz, ...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Monthly cost of utilities** (electricity, gas, ...)</t>
+    <t xml:space="preserve">**Montant mensuel des services publics** (électricité, gaz, parking, ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Monthly cost of utilities** (electricity, gas, parking, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">askForUtilitiesCustomConditional</t>
@@ -3932,7 +3932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="41" t="s">
         <v>115</v>
       </c>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
